--- a/doc/4-10#五菱/点位信息.xlsx
+++ b/doc/4-10#五菱/点位信息.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
     <t>下发公式</t>
   </si>
   <si>
-    <t>ABS工位</t>
+    <t>四分厂4-10-ABS</t>
   </si>
   <si>
     <t>192.168.0.1</t>
@@ -101,7 +101,7 @@
     <t>ABS检测SN</t>
   </si>
   <si>
-    <t>旋铆工位</t>
+    <t>四分厂4-10-铆接和裂纹</t>
   </si>
   <si>
     <t>100.100.100.1</t>
@@ -143,7 +143,7 @@
     <t>旋铆检测SN</t>
   </si>
   <si>
-    <t>游隙工位</t>
+    <t>四分厂4-10-游隙</t>
   </si>
   <si>
     <t>192.168.3.39</t>
@@ -188,7 +188,7 @@
     <t>间隙</t>
   </si>
   <si>
-    <t>震动工位</t>
+    <t>四分厂4-10-震动</t>
   </si>
   <si>
     <t>192.168.3.250</t>
@@ -219,7 +219,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +234,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="新宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -715,137 +721,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -860,6 +866,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1187,13 +1196,13 @@
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="2" max="2" width="14.875" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="8.375" customWidth="1"/>
     <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.2583333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.875" customWidth="1"/>
     <col min="9" max="9" width="7.375" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
@@ -1202,7 +1211,7 @@
     <col min="14" max="14" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="14.25" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1238,14 +1247,14 @@
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:11">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
@@ -1257,23 +1266,23 @@
       <c r="G2" s="2">
         <v>140</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <v>1</v>
       </c>
       <c r="J2" s="2"/>
     </row>
     <row r="3" ht="14.25" spans="1:11">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -1285,23 +1294,23 @@
       <c r="G3" s="2">
         <v>141</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>1</v>
       </c>
       <c r="J3" s="2"/>
     </row>
     <row r="4" ht="14.25" spans="1:11">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1321,15 +1330,15 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" ht="14.25" spans="1:11">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -1341,23 +1350,23 @@
       <c r="G5" s="2">
         <v>142</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="6">
         <v>1</v>
       </c>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>21</v>
@@ -1369,23 +1378,23 @@
       <c r="G6" s="2">
         <v>143</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="6">
         <v>1</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" ht="14.25" spans="1:11">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2">
-        <v>3005</v>
+        <v>7005</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>22</v>
@@ -1406,7 +1415,7 @@
       <c r="J7" s="2"/>
     </row>
     <row r="8" ht="14.25" spans="1:11">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1425,16 +1434,16 @@
       <c r="G8" s="2">
         <v>18</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="6">
         <v>1</v>
       </c>
       <c r="J8" s="2"/>
     </row>
     <row r="9" ht="14.25" spans="1:11">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1453,16 +1462,16 @@
       <c r="G9" s="2">
         <v>19</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="6">
         <v>1</v>
       </c>
       <c r="J9" s="2"/>
     </row>
     <row r="10" ht="14.25" spans="1:11">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1490,7 +1499,7 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" ht="14.25" spans="1:11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1509,16 +1518,16 @@
       <c r="G11" s="2">
         <v>38</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="6">
         <v>1</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" ht="14.25" spans="1:11">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1537,16 +1546,16 @@
       <c r="G12" s="2">
         <v>39</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="6">
         <v>1</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1576,7 +1585,7 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1606,7 +1615,7 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1636,7 +1645,7 @@
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:11">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1664,14 +1673,14 @@
       <c r="J16" s="2"/>
     </row>
     <row r="17" ht="14.25" spans="1:10">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>39</v>
@@ -1683,23 +1692,23 @@
       <c r="G17" s="2">
         <v>205</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="6">
         <v>1</v>
       </c>
       <c r="J17" s="2"/>
     </row>
     <row r="18" ht="14.25" spans="1:10">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>40</v>
@@ -1711,23 +1720,23 @@
       <c r="G18" s="2">
         <v>206</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="6">
         <v>1</v>
       </c>
       <c r="J18" s="2"/>
     </row>
     <row r="19" ht="14.25" spans="1:10">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>41</v>
@@ -1747,15 +1756,15 @@
       </c>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" ht="14.25" spans="1:10">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:10">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>42</v>
@@ -1767,23 +1776,23 @@
       <c r="G20" s="2">
         <v>232</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="6">
         <v>1</v>
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" ht="14.25" spans="1:10">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:10">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>43</v>
@@ -1795,23 +1804,23 @@
       <c r="G21" s="2">
         <v>233</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="6">
         <v>1</v>
       </c>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>44</v>
@@ -1832,14 +1841,14 @@
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>45</v>
@@ -1860,14 +1869,14 @@
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>46</v>
@@ -1888,14 +1897,14 @@
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>47</v>
@@ -1916,14 +1925,14 @@
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>48</v>
@@ -1944,14 +1953,14 @@
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>49</v>
@@ -1972,14 +1981,14 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>50</v>
@@ -2000,14 +2009,14 @@
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="2">
-        <v>9000</v>
+        <v>4005</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>51</v>
@@ -2027,8 +2036,8 @@
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" ht="14.25" spans="1:10">
-      <c r="A30" t="s">
+    <row r="30" spans="1:10">
+      <c r="A30" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B30" t="s">
@@ -2046,15 +2055,15 @@
       <c r="G30" s="2">
         <v>10</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:10">
-      <c r="A31" t="s">
+      <c r="A31" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B31" t="s">
@@ -2072,15 +2081,15 @@
       <c r="G31" s="2">
         <v>11</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" t="s">
+      <c r="A32" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B32" t="s">
@@ -2106,7 +2115,7 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" t="s">
+      <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B33" t="s">
@@ -2132,7 +2141,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O32" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O33" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D33">

--- a/doc/4-10#五菱/点位信息.xlsx
+++ b/doc/4-10#五菱/点位信息.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="60">
   <si>
     <t>设备名称</t>
   </si>
@@ -119,55 +119,58 @@
     <t>铆接SN</t>
   </si>
   <si>
+    <t>铆接检测1高度</t>
+  </si>
+  <si>
+    <t>Int32</t>
+  </si>
+  <si>
+    <t>({0}/1000)</t>
+  </si>
+  <si>
+    <t>铆接成型高度</t>
+  </si>
+  <si>
+    <t>铆接检测2高度</t>
+  </si>
+  <si>
     <t>旋铆检测OK</t>
   </si>
   <si>
     <t>旋铆检测NG</t>
   </si>
   <si>
-    <t>旋铆检测1高度</t>
+    <t>旋铆检测SN</t>
+  </si>
+  <si>
+    <t>四分厂4-10-游隙</t>
+  </si>
+  <si>
+    <t>192.168.3.39</t>
+  </si>
+  <si>
+    <t>游隙1工位OK</t>
+  </si>
+  <si>
+    <t>游隙1工位NG</t>
+  </si>
+  <si>
+    <t>游隙1工位SN</t>
+  </si>
+  <si>
+    <t>游隙2工位OK</t>
+  </si>
+  <si>
+    <t>游隙2工位NG</t>
+  </si>
+  <si>
+    <t>游隙2工位SN</t>
+  </si>
+  <si>
+    <t>正间隙</t>
   </si>
   <si>
     <t>Int16</t>
-  </si>
-  <si>
-    <t>({0}/1000)</t>
-  </si>
-  <si>
-    <t>旋铆成型高度</t>
-  </si>
-  <si>
-    <t>旋铆检测2高度</t>
-  </si>
-  <si>
-    <t>旋铆检测SN</t>
-  </si>
-  <si>
-    <t>四分厂4-10-游隙</t>
-  </si>
-  <si>
-    <t>192.168.3.39</t>
-  </si>
-  <si>
-    <t>游隙1工位OK</t>
-  </si>
-  <si>
-    <t>游隙1工位NG</t>
-  </si>
-  <si>
-    <t>游隙1工位SN</t>
-  </si>
-  <si>
-    <t>游隙2工位OK</t>
-  </si>
-  <si>
-    <t>游隙2工位NG</t>
-  </si>
-  <si>
-    <t>游隙2工位SN</t>
-  </si>
-  <si>
-    <t>正间隙</t>
   </si>
   <si>
     <t>下负荷</t>
@@ -1274,7 +1277,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" ht="14.25" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1330,7 +1333,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" ht="14.25" spans="1:11">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -1358,7 +1361,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" ht="14.25" spans="1:11">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1386,7 +1389,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" ht="14.25" spans="1:11">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1470,7 +1473,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" ht="14.25" spans="1:11">
+    <row r="10" spans="1:11">
       <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
@@ -1498,7 +1501,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" ht="14.25" spans="1:11">
+    <row r="11" spans="1:11">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -1513,20 +1516,22 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G11" s="2">
-        <v>38</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="6">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" ht="14.25" spans="1:11">
+        <v>1800</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1537,24 +1542,26 @@
         <v>7001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2">
-        <v>39</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="6">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:11">
+        <v>1804</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:11">
       <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
@@ -1565,26 +1572,26 @@
         <v>7001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="2">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:11">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -1599,22 +1606,20 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G14" s="2">
-        <v>1804</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>38</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:11">
       <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
@@ -1629,20 +1634,18 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2">
-        <v>1808</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" ht="14.25" spans="1:11">
       <c r="A16" s="5" t="s">
@@ -1662,7 +1665,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="2">
-        <v>17644</v>
+        <v>1744</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>19</v>
@@ -1756,7 +1759,7 @@
       </c>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" ht="14.25" spans="1:10">
       <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
@@ -1784,7 +1787,7 @@
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" ht="14.25" spans="1:10">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -1861,7 +1864,7 @@
         <v>900</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I23" s="2">
         <v>1</v>
@@ -1879,7 +1882,7 @@
         <v>4005</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
@@ -1889,7 +1892,7 @@
         <v>902</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -1907,7 +1910,7 @@
         <v>4005</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
@@ -1917,7 +1920,7 @@
         <v>906</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -1935,7 +1938,7 @@
         <v>4005</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
@@ -1945,7 +1948,7 @@
         <v>916</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I26" s="2">
         <v>1</v>
@@ -1963,7 +1966,7 @@
         <v>4005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
@@ -1973,7 +1976,7 @@
         <v>914</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -1991,7 +1994,7 @@
         <v>4005</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
@@ -2001,14 +2004,14 @@
         <v>918</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I28" s="2">
         <v>1</v>
       </c>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" ht="14.25" spans="1:10">
       <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2019,7 +2022,7 @@
         <v>4005</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
@@ -2029,28 +2032,28 @@
         <v>306</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" ht="14.25" spans="1:10">
       <c r="A30" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2">
         <v>9000</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G30" s="2">
         <v>10</v>
@@ -2064,22 +2067,22 @@
     </row>
     <row r="31" ht="14.25" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="2">
         <v>9000</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="G31" s="2">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>15</v>
@@ -2090,16 +2093,16 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" s="2">
         <v>9000</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
@@ -2116,16 +2119,16 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" s="2">
         <v>9000</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>18</v>

--- a/doc/4-10#五菱/点位信息.xlsx
+++ b/doc/4-10#五菱/点位信息.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="14.25" spans="1:11">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" ht="14.25" spans="1:11">
+    <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" ht="14.25" spans="1:11">
+    <row r="16" spans="1:11">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="2">
-        <v>1744</v>
+        <v>1764</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>19</v>
@@ -1749,7 +1749,7 @@
         <v>18</v>
       </c>
       <c r="G19" s="2">
-        <v>1824</v>
+        <v>1864</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>19</v>
@@ -1833,7 +1833,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="2">
-        <v>1864</v>
+        <v>1884</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>19</v>

--- a/doc/4-10#五菱/点位信息.xlsx
+++ b/doc/4-10#五菱/点位信息.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\4-10#五菱\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
@@ -10,7 +15,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +35,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="62">
+  <si>
+    <t>设备编号</t>
+  </si>
   <si>
     <t>设备名称</t>
   </si>
@@ -39,6 +47,9 @@
   </si>
   <si>
     <t>PLC_Port</t>
+  </si>
+  <si>
+    <t>功能分类</t>
   </si>
   <si>
     <t>点位名称</t>
@@ -1196,26 +1207,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="8.375" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="10.2583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
-    <col min="9" max="9" width="7.375" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1"/>
-    <col min="14" max="14" width="25.625" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="6" width="24.5" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
+    <col min="8" max="8" width="7.125" customWidth="1"/>
+    <col min="9" max="9" width="10.2583333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="7.375" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="12.625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
+    <col min="16" max="16" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:11">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="14.25" spans="1:13">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1245,915 +1257,1048 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:11">
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:13">
       <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2">
         <v>7005</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2">
+        <v>140</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:13">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2">
-        <v>140</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:11">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>7005</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2">
+        <v>141</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" ht="14.25" spans="1:13">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2">
-        <v>141</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="6">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" ht="14.25" spans="1:11">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>7005</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2">
         <v>1524</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="2">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" ht="14.25" spans="1:11">
+      <c r="J4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="2">
+        <v>40</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:13">
       <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
         <v>7005</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2">
+        <v>142</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:13">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="2">
-        <v>142</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" ht="14.25" spans="1:11">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>7005</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2">
+        <v>143</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" ht="14.25" spans="1:13">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="2">
-        <v>143</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>7005</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="2">
         <v>1570</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="2">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" ht="14.25" spans="1:11">
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="2">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
         <v>7001</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="2">
+        <v>18</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" ht="14.25" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="2">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" ht="14.25" spans="1:11">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
         <v>7001</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="2">
+        <v>19</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="2">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>7001</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="2">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="2">
         <v>1724</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="2">
-        <v>20</v>
-      </c>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="J10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="2">
+        <v>40</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2">
         <v>7001</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="2">
+        <v>31</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="2">
         <v>1800</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2">
         <v>7001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="2">
+        <v>34</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="2">
         <v>1804</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:11">
+        <v>32</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:13">
       <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2">
         <v>7001</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="2">
+        <v>35</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="2">
         <v>1808</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:11">
+        <v>32</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:13">
       <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2">
         <v>7001</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="2">
+        <v>38</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:13">
+      <c r="A15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="2">
-        <v>38</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="6">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" ht="14.25" spans="1:11">
-      <c r="A15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="D15" s="2">
         <v>7001</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="2">
+        <v>39</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:13">
+      <c r="A16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="2">
-        <v>39</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="6">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>7001</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="2">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="2">
         <v>1764</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="2">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" ht="14.25" spans="1:10">
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="2">
+        <v>40</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:12">
       <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="2">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2">
         <v>4005</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="2">
+        <v>41</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="2">
         <v>205</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="6">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" ht="14.25" spans="1:10">
+      <c r="J17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" ht="14.25" spans="1:12">
       <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="2">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="2">
         <v>4005</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="2">
+        <v>42</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="2">
         <v>206</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="6">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" ht="14.25" spans="1:10">
+      <c r="J18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="6">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" ht="14.25" spans="1:12">
       <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="2">
         <v>4005</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="2">
+        <v>43</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="2">
         <v>1864</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="2">
-        <v>20</v>
-      </c>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" ht="14.25" spans="1:10">
+      <c r="J19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="2">
+        <v>40</v>
+      </c>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" ht="14.25" spans="1:12">
       <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="2">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2">
         <v>4005</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="2">
+        <v>44</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="2">
         <v>232</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="6">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:10">
+      <c r="J20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" ht="14.25" spans="1:12">
       <c r="A21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="2">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="2">
         <v>4005</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="2">
+        <v>45</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="2">
         <v>233</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="6">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="J21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="2">
+        <v>39</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="2">
         <v>4005</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="2">
+        <v>46</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="2">
         <v>1884</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="2">
-        <v>20</v>
-      </c>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="J22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="2">
+        <v>40</v>
+      </c>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="2">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="2">
         <v>4005</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="2">
+        <v>47</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="2">
         <v>900</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="J23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="2">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="2">
         <v>4005</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="2">
+        <v>49</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="2">
         <v>902</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="2">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="2">
         <v>4005</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="2">
+        <v>50</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="2">
         <v>906</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="2">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="2">
         <v>4005</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="2">
+        <v>51</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="2">
         <v>916</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="2">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="2">
         <v>4005</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="2">
+        <v>52</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="2">
         <v>914</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="2">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="2">
         <v>4005</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="2">
+        <v>53</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="2">
         <v>918</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:10">
+      <c r="J28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" ht="14.25" spans="1:12">
       <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="2">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="2">
         <v>4005</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="2">
+        <v>54</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="2">
         <v>306</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:10">
+      <c r="J29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" ht="14.25" spans="1:12">
       <c r="A30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="2">
+        <v>55</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="2">
         <v>9000</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="2">
+        <v>10</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="1:12">
+      <c r="A31" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F30" t="s">
+      <c r="B31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="2">
-        <v>10</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:10">
-      <c r="A31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="D31" s="2">
         <v>9000</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="2">
         <v>50</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="2">
+        <v>55</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="2">
         <v>9000</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="2">
+        <v>60</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="2">
         <v>1920</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="2">
+      <c r="J32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="2">
+        <v>9000</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="2">
-        <v>9000</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="I33" s="2">
         <v>1900</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="2">
-        <v>20</v>
+      <c r="J33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="2">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:Q33" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="D33">
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D7">
+  <conditionalFormatting sqref="F5:F7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D4 D8:D32 D34:D1048576">
+  <conditionalFormatting sqref="F1:F4 F8:F32 F34:F1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
